--- a/StructureDefinition-HivEncounter.xlsx
+++ b/StructureDefinition-HivEncounter.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T15:35:56+00:00</t>
+    <t>2025-01-13T20:12:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HivEncounter.xlsx
+++ b/StructureDefinition-HivEncounter.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.4.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T20:12:32+00:00</t>
+    <t>2025-01-30T04:55:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HivEncounter.xlsx
+++ b/StructureDefinition-HivEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-30T04:55:08+00:00</t>
+    <t>2025-01-31T22:08:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HivEncounter.xlsx
+++ b/StructureDefinition-HivEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T22:08:22+00:00</t>
+    <t>2025-02-01T06:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HivEncounter.xlsx
+++ b/StructureDefinition-HivEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T06:47:49+00:00</t>
+    <t>2025-02-01T23:07:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HivEncounter.xlsx
+++ b/StructureDefinition-HivEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T23:07:45+00:00</t>
+    <t>2025-02-01T23:40:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HivEncounter.xlsx
+++ b/StructureDefinition-HivEncounter.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.1</t>
+    <t>0.4.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T23:40:00+00:00</t>
+    <t>2025-02-02T03:11:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HivEncounter.xlsx
+++ b/StructureDefinition-HivEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-02T03:11:41+00:00</t>
+    <t>2025-03-10T17:41:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
